--- a/fixtures/acfc_shapes/sttm/pair_11_family_b.xlsx
+++ b/fixtures/acfc_shapes/sttm/pair_11_family_b.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Decimal(18,2)</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Decimal(18,2)</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Decimal(18,0)</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Decimal(18,0)</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Decimal(18,4)</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>Decimal(18,4)</t>
         </is>
       </c>
     </row>
